--- a/output/pdf_financials_xlsx/PVIS.xlsx
+++ b/output/pdf_financials_xlsx/PVIS.xlsx
@@ -2541,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.334217</v>
+        <v>0.497527</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
@@ -4969,7 +4969,11 @@
           <t>Warrant reserve (note 5)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PVIS.xlsx
+++ b/output/pdf_financials_xlsx/PVIS.xlsx
@@ -681,19 +681,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-5.6e-05</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.017225</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.011927</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.003907</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.002346</v>
       </c>
     </row>
     <row r="13">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.018944</v>
+        <v>-0.018888</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.018944</v>
+        <v>-0.036169</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.018944</v>
+        <v>-0.018888</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.018944</v>
+        <v>-0.036169</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.000056</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>1.200655</v>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.000056</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>1.200655</v>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7335,7 +7335,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">

--- a/output/pdf_financials_xlsx/PVIS.xlsx
+++ b/output/pdf_financials_xlsx/PVIS.xlsx
@@ -1375,10 +1375,10 @@
         <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.064123</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.119644</v>
       </c>
     </row>
     <row r="41">
@@ -1397,10 +1397,10 @@
         <v>0</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.08654100000000001</v>
+        <v>0.150664</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.517433</v>
+        <v>0.637077</v>
       </c>
     </row>
     <row r="42">
@@ -1551,10 +1551,10 @@
         <v>0.035003</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.052098</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.064218</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1980,13 +1980,13 @@
         <v>0.012301</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.383216</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.226422</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.143882</v>
       </c>
     </row>
     <row r="68">
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-8.6e-05</v>
       </c>
       <c r="E121" s="3" t="n">
         <v>0</v>
@@ -6076,7 +6076,11 @@
           <t>Repurchase of shares 10</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
